--- a/artfynd/A 26216-2026 artfynd.xlsx
+++ b/artfynd/A 26216-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97760922</v>
+        <v>97760925</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,47 +686,52 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Krokom, NO Glåmnäsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460679.5575665803</v>
+        <v>460678</v>
       </c>
       <c r="R2" t="n">
-        <v>7063296.899243148</v>
+        <v>7063301</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 26216-2026 artfynd.xlsx
+++ b/artfynd/A 26216-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,8 +799,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97760925</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>